--- a/artfynd/S 2443-2023 artfynd.xlsx
+++ b/artfynd/S 2443-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY297"/>
+  <dimension ref="A1:AZ297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101758738</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
           <t>Floraväkteri C-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80086</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
           <t>Floraväkteri C-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83921</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72164186</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101758715</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1335,6 +1365,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108101759</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1455,6 +1490,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/260413</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1568,6 +1608,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/262991</t>
         </is>
       </c>
     </row>
@@ -1675,6 +1720,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64353497</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1780,6 +1830,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64629105</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1882,6 +1937,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074303</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1983,6 +2043,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99695708</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2124,6 +2189,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95062180</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2265,6 +2335,11 @@
       <c r="AY15" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95462491</t>
         </is>
       </c>
     </row>
@@ -2369,6 +2444,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108101656</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2470,6 +2550,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108101819</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2571,6 +2656,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108101778</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2687,6 +2777,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102949009</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2789,6 +2884,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101758676</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2905,6 +3005,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102949008</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3012,6 +3117,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75796255</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3128,6 +3238,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102949018</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3243,6 +3358,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95062018</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3378,6 +3498,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95062058</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3503,6 +3628,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95062269</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3628,6 +3758,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95492452</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3753,6 +3888,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95492754</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3878,6 +4018,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95492805</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4001,6 +4146,11 @@
       <c r="AY30" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95492970</t>
         </is>
       </c>
     </row>
@@ -4105,6 +4255,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101758673</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4220,6 +4375,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102949012</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4319,6 +4479,11 @@
       <c r="AY33" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102949019</t>
         </is>
       </c>
     </row>
@@ -4436,6 +4601,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102949023</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4571,6 +4741,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95062115</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4696,6 +4871,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95062261</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4831,6 +5011,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95462250</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4969,6 +5154,11 @@
       <c r="AY38" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95462278</t>
         </is>
       </c>
     </row>
@@ -5073,6 +5263,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101758666</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5188,6 +5383,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102949013</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5289,6 +5489,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102949017</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5388,6 +5593,11 @@
       <c r="AY42" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102949020</t>
         </is>
       </c>
     </row>
@@ -5501,6 +5711,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102949007</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5616,6 +5831,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102949011</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5731,6 +5951,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102949014</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5846,6 +6071,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102949021</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5965,6 +6195,11 @@
       <c r="AY47" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102949022</t>
         </is>
       </c>
     </row>
@@ -6069,6 +6304,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101758698</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6192,6 +6432,11 @@
       <c r="AY49" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95492449</t>
         </is>
       </c>
     </row>
@@ -6296,6 +6541,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101758680</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6412,6 +6662,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102949015</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6529,6 +6784,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112496622</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6672,6 +6932,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95493274</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6812,6 +7077,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95062357</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6951,6 +7221,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95461379</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7094,6 +7369,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95462402</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7232,6 +7512,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95462484</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7375,6 +7660,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95462565</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7513,6 +7803,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95467802</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7651,6 +7946,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95467865</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7789,6 +8089,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95467958</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7927,6 +8232,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95493313</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8065,6 +8375,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95493363</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8173,6 +8488,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112510296</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8274,6 +8594,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108101736</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8393,6 +8718,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95062272</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8508,6 +8838,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72164354</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8610,6 +8945,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75796262</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8725,6 +9065,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95062144</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8831,6 +9176,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102948973</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8941,6 +9291,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72164334</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9056,6 +9411,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95062137</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9171,6 +9531,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95062278</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9288,6 +9653,11 @@
       <c r="AY74" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95493449</t>
         </is>
       </c>
     </row>
@@ -9396,6 +9766,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102948972</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9502,6 +9877,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102948975</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9618,6 +9998,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95062491</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9728,6 +10113,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074316</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9848,6 +10238,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95062480</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9967,6 +10362,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95071917</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10084,6 +10484,11 @@
       <c r="AY81" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95493460</t>
         </is>
       </c>
     </row>
@@ -10192,6 +10597,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102948971</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10298,6 +10708,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102948976</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10413,6 +10828,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72164320</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10528,6 +10948,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95062333</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10634,6 +11059,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102948974</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10740,6 +11170,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102948977</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10852,6 +11287,11 @@
       <c r="AY88" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102949183</t>
         </is>
       </c>
     </row>
@@ -10979,6 +11419,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102949340</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11092,6 +11537,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110572513</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11200,6 +11650,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110572538</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11308,6 +11763,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110572028</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11416,6 +11876,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110572543</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11524,6 +11989,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110573172</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11632,6 +12102,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110572517</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11740,6 +12215,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110572632</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11856,6 +12336,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1868567</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11964,6 +12449,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110572718</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12072,6 +12562,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110573004</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12180,6 +12675,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110573168</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12288,6 +12788,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112816214</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12389,6 +12894,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292309</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12490,6 +13000,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292400</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12606,6 +13121,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292466</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12722,6 +13242,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292504</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12823,6 +13348,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292515</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12924,6 +13454,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292543</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13040,6 +13575,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292586</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13141,6 +13681,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292612</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13261,6 +13806,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75732703</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13362,6 +13912,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292384</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13463,6 +14018,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292564</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13563,6 +14123,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64629303</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13686,6 +14251,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72909979</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13809,6 +14379,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73060581</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13932,6 +14507,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73060837</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -14055,6 +14635,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73063510</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14152,6 +14737,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117722412</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14272,6 +14862,11 @@
           <t>Floraväkteri C-län</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/263492</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14391,6 +14986,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72812416</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14519,6 +15119,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73060681</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14640,6 +15245,11 @@
       <c r="AY122" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73063543</t>
         </is>
       </c>
     </row>
@@ -14745,6 +15355,11 @@
       <c r="AY123" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75732307</t>
         </is>
       </c>
     </row>
@@ -14849,6 +15464,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292415</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14951,6 +15571,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292528</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -15049,6 +15674,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112533222</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15149,6 +15779,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64629143</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15249,6 +15884,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99870096</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15349,6 +15989,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64629337</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15492,6 +16137,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72169217</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15635,6 +16285,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72169348</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15778,6 +16433,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72169474</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15917,6 +16577,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72170241</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -16060,6 +16725,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72170429</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -16202,6 +16872,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72909992</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16332,6 +17007,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75732457</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16440,6 +17120,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112499462</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16538,6 +17223,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112533258</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16639,6 +17329,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292567</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16747,6 +17442,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106141014</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16848,6 +17548,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292596</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16987,6 +17692,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72170250</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -17125,6 +17835,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72170320</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -17254,6 +17969,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72481572</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -17393,6 +18113,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72169265</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17532,6 +18257,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72170263</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17658,6 +18388,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75732456</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17760,6 +18495,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292305</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17889,6 +18629,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72481590</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -18001,6 +18746,11 @@
       <c r="AY150" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75732458</t>
         </is>
       </c>
     </row>
@@ -18105,6 +18855,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074336</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -18206,6 +18961,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292299</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -18307,6 +19067,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292403</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -18406,6 +19171,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64629350</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -18540,6 +19310,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72910002</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18660,6 +19435,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72481449</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18765,6 +19545,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75732305</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18875,6 +19660,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75732306</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18990,6 +19780,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72481840</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -19092,6 +19887,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292250</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -19207,6 +20007,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72481438</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -19322,6 +20127,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72481856</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -19443,6 +20253,11 @@
       <c r="AY163" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73060777</t>
         </is>
       </c>
     </row>
@@ -19550,6 +20365,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75732308</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19665,6 +20485,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72481878</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19768,6 +20593,11 @@
       <c r="AY166" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75732304</t>
         </is>
       </c>
     </row>
@@ -19872,6 +20702,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292289</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19987,6 +20822,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72481404</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -20102,6 +20942,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72481866</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -20221,6 +21066,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72169431</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -20336,6 +21186,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72481826</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -20441,6 +21296,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75732309</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20559,6 +21419,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112555350</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20660,6 +21525,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074389</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20768,6 +21638,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106141573</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20900,6 +21775,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106141824</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -21024,6 +21904,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074415</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -21122,6 +22007,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142015</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -21230,6 +22120,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142873</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -21332,6 +22227,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117722411</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -21455,6 +22355,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72857219</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -21580,6 +22485,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/220756</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -21700,6 +22610,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/222796</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21823,6 +22738,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72876032</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21942,6 +22862,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72876126</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -22065,6 +22990,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72909820</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -22188,6 +23118,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73056110</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -22311,6 +23246,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73058304</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -22432,6 +23372,11 @@
       <c r="AY189" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80442557</t>
         </is>
       </c>
     </row>
@@ -22536,6 +23481,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074381</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -22638,6 +23588,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292224</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -22754,6 +23709,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116351195</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -22878,6 +23838,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72856802</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -23002,6 +23967,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72876170</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -23126,6 +24096,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72879055</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -23250,6 +24225,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80454985</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -23376,6 +24356,11 @@
       <c r="AY197" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80650216</t>
         </is>
       </c>
     </row>
@@ -23480,6 +24465,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074398</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -23595,6 +24585,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82002931</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -23742,6 +24737,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72859593</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -23884,6 +24884,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72865301</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -24026,6 +25031,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72879005</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -24169,6 +25179,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73025767</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -24307,6 +25322,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73028963</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -24451,6 +25471,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73029026</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -24595,6 +25620,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80442414</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -24739,6 +25769,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80442711</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -24887,6 +25922,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80650355</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -25031,6 +26071,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80650395</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -25129,6 +26174,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142008</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -25237,6 +26287,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142220</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -25345,6 +26400,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142800</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -25478,6 +26538,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72876066</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -25609,6 +26674,11 @@
       <c r="AY214" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72879101</t>
         </is>
       </c>
     </row>
@@ -25712,6 +26782,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292155</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -25854,6 +26929,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72857052</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -25989,6 +27069,11 @@
       <c r="AY217" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73028259</t>
         </is>
       </c>
     </row>
@@ -26107,6 +27192,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82007284</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -26236,6 +27326,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72865357</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -26374,6 +27469,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72875224</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -26512,6 +27612,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72878878</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -26654,6 +27759,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73028966</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -26789,6 +27899,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80509458</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -26933,6 +28048,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80650363</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -27041,6 +28161,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142172</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -27155,6 +28280,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72875159</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -27289,6 +28419,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72875981</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -27423,6 +28558,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72878893</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -27560,6 +28700,11 @@
       <c r="AY229" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73058247</t>
         </is>
       </c>
     </row>
@@ -27693,6 +28838,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80509219</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -27828,6 +28978,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80509265</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -27963,6 +29118,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80649892</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -28096,6 +29256,11 @@
       <c r="AY233" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80649933</t>
         </is>
       </c>
     </row>
@@ -28214,6 +29379,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81989698</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -28340,6 +29510,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81989746</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -28473,6 +29648,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72860430</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -28601,6 +29781,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72875231</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -28725,6 +29910,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73045130</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -28854,6 +30044,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73045316</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -28982,6 +30177,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73056398</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -29104,6 +30304,11 @@
       <c r="AY241" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73057785</t>
         </is>
       </c>
     </row>
@@ -29208,6 +30413,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292207</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -29342,6 +30552,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73025763</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -29486,6 +30701,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80442909</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -29615,6 +30835,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72876023</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -29735,6 +30960,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81989509</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -29863,6 +31093,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72859853</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -29980,6 +31215,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73056021</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -30111,6 +31351,11 @@
       <c r="AY249" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73058436</t>
         </is>
       </c>
     </row>
@@ -30214,6 +31459,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292192</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -30312,6 +31562,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142016</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -30413,6 +31668,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103292175</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -30546,6 +31806,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72850415</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -30684,6 +31949,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72859477</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -30822,6 +32092,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73056541</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -30959,6 +32234,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72865402</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -31086,6 +32366,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72876198</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -31225,6 +32510,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80650039</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -31362,6 +32652,11 @@
       <c r="AY259" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80650386</t>
         </is>
       </c>
     </row>
@@ -31489,6 +32784,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82005960</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -31587,6 +32887,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142012</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -31700,6 +33005,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142153</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -31798,6 +33108,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142009</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -31906,6 +33221,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106142796</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -32032,6 +33352,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15437</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -32163,6 +33488,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73028737</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -32290,6 +33620,11 @@
       <c r="AY267" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80454870</t>
         </is>
       </c>
     </row>
@@ -32394,6 +33729,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102074400</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -32522,6 +33862,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73047731</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -32650,6 +33995,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73055792</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -32769,6 +34119,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72875316</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -32897,6 +34252,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80470990</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -33021,6 +34381,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80650314</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -33140,6 +34505,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72832801</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -33259,6 +34629,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72875168</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -33378,6 +34753,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72876127</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -33495,6 +34875,11 @@
       <c r="AY277" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73029083</t>
         </is>
       </c>
     </row>
@@ -33608,6 +34993,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80509421</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -33727,6 +35117,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80649867</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -33851,6 +35246,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80650321</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -33959,6 +35359,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106141549</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -34070,6 +35475,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73056471</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -34189,6 +35599,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72865309</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -34308,6 +35723,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72875175</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -34427,6 +35847,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80649847</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -34546,6 +35971,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72832785</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -34665,6 +36095,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73057921</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -34784,6 +36219,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80509433</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -34903,6 +36343,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80649856</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -35027,6 +36472,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80650328</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -35146,6 +36596,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72865322</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -35265,6 +36720,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72875185</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -35379,6 +36839,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72876208</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -35498,6 +36963,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73055731</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -35621,6 +37091,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80509150</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -35740,6 +37215,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80649840</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -35863,8 +37343,311 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72865326</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>